--- a/content-files/Math1.xlsx
+++ b/content-files/Math1.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,11 +498,6 @@
           <t>License</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Unnamed: 16</t>
-        </is>
-      </c>
       <c r="R1" t="inlineStr">
         <is>
           <t>Validator Check</t>
@@ -560,6 +555,529 @@
           <t>Evaluate f(x) = x**2 +3x - 4 at:</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/1-1-functions-and-function-notation</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Evaluation of Functions in algebra Forms in Openstax Precalc</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Evaluation of Functions in algebra Forms in Openstax Precalc</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>No errors found</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>26/08/2026 16:13:50</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/ab2f376functions8</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>ab2f376functions8</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>6P9VvrLo-vp41-vhVxNonOxt</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>showStuMastery: false</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>functions8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Evaluate (f(a+h)-f(a))/h</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2a+h+3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>doMasteryUpdate: false</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>functions8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Use the answers to your previous parts-- you already have f(a+h) and f(a)!</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>keepMCOrder: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>functions8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Simplifying the numerator</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>What is f(a+h)-f(a)?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2ah+h**2 + 3h</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>allowRecycle: false</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>functions8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Final step</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Now divide all terms by h.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>giveStuHints: false</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>quadratic16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>problem</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Applying the Vertex of a Parabola</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A ball is thrown upward from the top of a 40 foot high building at a speed of 80 feet per second. The ball’s height above ground can be modeled by the equation H(t)=-16t**2+80t+40.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/3-2-quadratic-functions</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Quadratic Functions</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Quadratic Functions</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>openstax</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/ &lt;CC BY 4.0&gt;</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/ab2f376quadratic16</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>ab2f376quadratic16</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>fixedProblemOrder: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>quadratic16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What is the maximum height of the ball in feet?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>chat_display_mode: Window</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>quadratic16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Calculate Maximum Height</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>To find maximum height, find the y-coordinate of the vertex of the parabola.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>quadratic16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Identify Max Height</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The maximum height can be found by plugging in the x-coordinate from what time the max ball height is reached.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>quadratic16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>X-coordinate of Vertex</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>The x-coordinate is given by the value of -b/2a. Plug in to the function to find the value of the maximum height.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Problem Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Row Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Body Text</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>answerType</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>HintID</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>mcChoices</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Images (space delimited)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OER src</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>openstax KC</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Validator Check</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Time Last Checked</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Debug Link</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Problem ID</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Lesson ID</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Image Checksum</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>functions30</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>problem</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Given the function f(x) = 8 - 3x:</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -585,11 +1103,31 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>No errors found</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>26/08/2026 16:13:50</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/ab29bf1functions30</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>ab29bf1functions30</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1fipQkal-zr8g-CP1xQby4l2</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
@@ -600,7 +1138,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>functions8</t>
+          <t>functions30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -610,13 +1148,13 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Evaluate (f(a+h)-f(a))/h</t>
+          <t>Solve for f(x) = -1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2a+h+3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -650,7 +1188,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>functions8</t>
+          <t>functions30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -660,10 +1198,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Use the answers to your previous parts-- you already have f(a+h) and f(a)!</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Setting up the equation</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This question is asking, what x value would satisfy the equation 8 - 3x = -1?</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
@@ -696,34 +1238,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>functions8</t>
+          <t>functions30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>scaffold</t>
+          <t>hint</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Simplifying the numerator</t>
+          <t>Solving the equation</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>What is f(a+h)-f(a)?</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2ah+h**2 + 3h</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
+          <t>Add 3x to both sides to get 8 = 3x-1. Then you can add 1 to both sides to get 9 = 3x.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>h2</t>
@@ -758,688 +1292,6 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>functions8</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Final step</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Now divide all terms by h.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>giveStuHints: false</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>quadratic16</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Applying the Vertex of a Parabola</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>A ball is thrown upward from the top of a 40 foot high building at a speed of 80 feet per second. The ball’s height above ground can be modeled by the equation H(t)=-16t**2+80t+40.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/3-2-quadratic-functions</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Quadratic Functions</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Quadratic Functions</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>openstax</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/ &lt;CC BY 4.0&gt;</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>fixedProblemOrder: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>quadratic16</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>What is the maximum height of the ball in feet?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="n">
-        <v>140</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>chat_display_mode: Window</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>quadratic16</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Calculate Maximum Height</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>To find maximum height, find the y-coordinate of the vertex of the parabola.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>quadratic16</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Identify Max Height</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>The maximum height can be found by plugging in the x-coordinate from what time the max ball height is reached.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>quadratic16</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>X-coordinate of Vertex</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>The x-coordinate is given by the value of -b/2a. Plug in to the function to find the value of the maximum height.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:X12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Problem Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Row Type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Body Text</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>answerType</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>HintID</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Dependency</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>mcChoices</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Images (space delimited)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Parent</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>OER src</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>openstax KC</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Taxonomy</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>License</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Unnamed: 16</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Validator Check</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Time Last Checked</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Debug Link</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Problem ID</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Lesson ID</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Image Checksum</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>functions30</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Given the function f(x) = 8 - 3x:</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/1-1-functions-and-function-notation</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Evaluation of Functions in algebra Forms in Openstax Precalc</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Evaluation of Functions in algebra Forms in Openstax Precalc</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>showStuMastery: false</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>functions30</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Solve for f(x) = -1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>doMasteryUpdate: false</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>functions30</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Setting up the equation</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>This question is asking, what x value would satisfy the equation 8 - 3x = -1?</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>keepMCOrder: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>functions30</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Solving the equation</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Add 3x to both sides to get 8 = 3x-1. Then you can add 1 to both sides to get 9 = 3x.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>allowRecycle: false</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
           <t>quadratic26</t>
         </is>
       </c>
@@ -1493,8 +1345,16 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/ab29bf1quadratic26</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>ab29bf1quadratic26</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
@@ -1520,8 +1380,10 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
-        <v>7</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1676,8 +1538,10 @@
           <t>What is the x-coordinate value calculated from the formula?</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>2</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,32 +1625,6 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content-files/Math1.xlsx
+++ b/content-files/Math1.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,11 @@
           <t>License</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
       <c r="R1" t="inlineStr">
         <is>
           <t>Validator Check</t>
@@ -537,7 +542,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>functions8</t>
+          <t>vector3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -547,534 +552,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Evaluating Functions at Specific Values</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Evaluate f(x) = x**2 +3x - 4 at:</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/1-1-functions-and-function-notation</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Evaluation of Functions in algebra Forms in Openstax Precalc</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Evaluation of Functions in algebra Forms in Openstax Precalc</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>No errors found</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>26/08/2026 16:13:50</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/ab2f376functions8</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>ab2f376functions8</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>6P9VvrLo-vp41-vhVxNonOxt</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>showStuMastery: false</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>functions8</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Evaluate (f(a+h)-f(a))/h</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2a+h+3</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>doMasteryUpdate: false</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>functions8</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Use the answers to your previous parts-- you already have f(a+h) and f(a)!</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>keepMCOrder: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>functions8</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>scaffold</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Simplifying the numerator</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>What is f(a+h)-f(a)?</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2ah+h**2 + 3h</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>allowRecycle: false</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>functions8</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Final step</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Now divide all terms by h.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>giveStuHints: false</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>quadratic16</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Applying the Vertex of a Parabola</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>A ball is thrown upward from the top of a 40 foot high building at a speed of 80 feet per second. The ball’s height above ground can be modeled by the equation H(t)=-16t**2+80t+40.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/3-2-quadratic-functions</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Quadratic Functions</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Quadratic Functions</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>openstax</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/4.0/ &lt;CC BY 4.0&gt;</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/ab2f376quadratic16</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>ab2f376quadratic16</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>fixedProblemOrder: true</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>quadratic16</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>What is the maximum height of the ball in feet?</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>algebra</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>chat_display_mode: Window</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>quadratic16</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Calculate Maximum Height</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>To find maximum height, find the y-coordinate of the vertex of the parabola.</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>quadratic16</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Identify Max Height</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>The maximum height can be found by plugging in the x-coordinate from what time the max ball height is reached.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>quadratic16</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>hint</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>X-coordinate of Vertex</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>The x-coordinate is given by the value of -b/2a. Plug in to the function to find the value of the maximum height.</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:X11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Problem Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Row Type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Body Text</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>answerType</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>HintID</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Dependency</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>mcChoices</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Images (space delimited)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Parent</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>OER src</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>openstax KC</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Taxonomy</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>License</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Validator Check</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Time Last Checked</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Debug Link</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Problem ID</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Lesson ID</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Image Checksum</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>functions30</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>problem</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Given the function f(x) = 8 - 3x:</t>
+          <t>Magnitude and Direction</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1087,45 +565,33 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://openstax.org/books/precalculus-2e/pages/1-1-functions-and-function-notation</t>
+          <t>https://openstax.org/books/precalculus-2e/pages/8-8-vectors</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Evaluation of Functions in algebra Forms in Openstax Precalc</t>
+          <t>Vectors</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Evaluation of Functions in algebra Forms in Openstax Precalc</t>
+          <t>openstax</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/ &lt;CC BY 4.0&gt;</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>No errors found</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>26/08/2026 16:13:50</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/ab29bf1functions30</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>ab29bf1functions30</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1fipQkal-zr8g-CP1xQby4l2</t>
+          <t>6P9VvrLo-vp41-vhVxNonOxt</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
@@ -1138,7 +604,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>functions30</t>
+          <t>vector3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1148,13 +614,13 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Solve for f(x) = -1</t>
+          <t>Find the magnitude of the vector with initial point P(-8,1) and terminal point Q(-2,-5).</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6√2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1188,7 +654,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>functions30</t>
+          <t>vector3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1198,12 +664,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Setting up the equation</t>
+          <t>Find Position Vector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>This question is asking, what x value would satisfy the equation 8 - 3x = -1?</t>
+          <t>For an initial point (x1, y1) and terminal point (x2, y2), the position vector is ⟨x2-x1, y2-y1⟩.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1238,7 +704,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>functions30</t>
+          <t>vector3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1248,12 +714,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Solving the equation</t>
+          <t>Identify Variables</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Add 3x to both sides to get 8 = 3x-1. Then you can add 1 to both sides to get 9 = 3x.</t>
+          <t>x1=-8, y1=1, x2=-2, y2=-5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1292,6 +758,938 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>vector3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Substitute</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>⟨x2-x1, y2-y1⟩=⟨-2-(-8), -5-1⟩</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>giveStuHints: false</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>vector3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Simplify ⟨-2-(-8), -5-1⟩:</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>⟨6, -6⟩</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>mc</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>⟨6, -6⟩|⟨6, -6⟩|⟨10, 6⟩|⟨10, 4⟩</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>fixedProblemOrder: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>vector3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Find Magnitude</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>How do we find the magnitude of a vector?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>√(a**2+b**2)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>mc</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>h4</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>a+b|√(a**2+b**2)|3√(a**3+b**3)|a**2+b*82</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>chat_display_mode: Window</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>vector3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Substitute</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Substitute and find the magnitude of the vector, unsimplified.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>√72</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>h4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>vector3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>scaffold</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Simplify √72. Hint: can we take out any perfect squares?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6√2</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>h4</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>quadratic16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>problem</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Applying the Vertex of a Parabola</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A ball is thrown upward from the top of a 40 foot high building at a speed of 80 feet per second. The ball’s height above ground can be modeled by the equation H(t)=-16t**2+80t+40.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/3-2-quadratic-functions</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Quadratic Functions</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Quadratic Functions</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>openstax</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/ &lt;CC BY 4.0&gt;</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>quadratic16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>What is the maximum height of the ball in feet?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>140</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>quadratic16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Calculate Maximum Height</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>To find maximum height, find the y-coordinate of the vertex of the parabola.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>quadratic16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Identify Max Height</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>The maximum height can be found by plugging in the x-coordinate from what time the max ball height is reached.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>quadratic16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>X-coordinate of Vertex</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>The x-coordinate is given by the value of -b/2a. Plug in to the function to find the value of the maximum height.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Problem Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Row Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Body Text</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>answerType</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>HintID</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>mcChoices</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Images (space delimited)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OER src</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>openstax KC</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Taxonomy</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Unnamed: 16</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Validator Check</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Time Last Checked</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Debug Link</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Problem ID</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Lesson ID</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Image Checksum</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>vector8</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>problem</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Operations on Vectors</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://openstax.org/books/precalculus-2e/pages/8-8-vectors</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Vectors</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>openstax</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/ &lt;CC BY 4.0&gt;</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1fipQkal-zr8g-CP1xQby4l2</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>showStuMastery: false</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>vector8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Use the vectors u = i+5j, v = -2i-3j, and w = 4i-j to find u+(v-w).</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-5i+3j</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>algebra</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>doMasteryUpdate: false</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>vector8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Substitute</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>i+5j+(-2i-3j-(4i-j))</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>keepMCOrder: true</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>vector8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Simplify</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>i+5j+(-2i-3j-(4i-j))=i+5j+(-2i-3j-4i+j))=i+5j+(-6i-2j)=-5i+3j</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>allowRecycle: false</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>quadratic26</t>
         </is>
       </c>
@@ -1345,16 +1743,8 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>https://cahlr.github.io/OATutor-Content-Staging/#/debug/ab29bf1quadratic26</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>ab29bf1quadratic26</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
@@ -1380,10 +1770,8 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
+      <c r="E7" t="n">
+        <v>7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1538,10 +1926,8 @@
           <t>What is the x-coordinate value calculated from the formula?</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="E10" t="n">
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1625,6 +2011,32 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
